--- a/data/trans_dic/P2C_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,52; 26,56</t>
+          <t>14,91; 26,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,28; 37,75</t>
+          <t>23,66; 39,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,8; 40,03</t>
+          <t>24,17; 40,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,07</t>
+          <t>1,0; 5,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,19; 40,62</t>
+          <t>27,06; 40,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,04; 61,74</t>
+          <t>48,31; 61,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,87; 64,97</t>
+          <t>51,29; 65,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 11,2</t>
+          <t>3,55; 10,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,33; 31,09</t>
+          <t>22,31; 31,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,34; 49,48</t>
+          <t>38,81; 48,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40,3; 51,22</t>
+          <t>40,24; 51,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,81</t>
+          <t>2,94; 7,04</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,46; 63,8</t>
+          <t>52,43; 63,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,95; 73,33</t>
+          <t>62,46; 73,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,88; 80,12</t>
+          <t>68,39; 79,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 11,88</t>
+          <t>5,27; 12,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,17; 80,55</t>
+          <t>72,41; 80,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,11; 94,46</t>
+          <t>89,05; 94,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,09; 89,96</t>
+          <t>83,45; 90,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,3; 20,88</t>
+          <t>10,2; 20,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65,4; 71,93</t>
+          <t>65,09; 72,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78,77; 84,57</t>
+          <t>78,96; 84,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78,34; 84,84</t>
+          <t>78,24; 84,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 15,52</t>
+          <t>9,6; 15,47</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,12; 64,35</t>
+          <t>55,73; 65,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,43; 77,81</t>
+          <t>71,02; 78,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,91; 75,81</t>
+          <t>67,69; 75,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,83; 20,66</t>
+          <t>13,62; 20,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65,49; 72,94</t>
+          <t>65,32; 73,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92,8; 96,54</t>
+          <t>93,06; 96,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,89; 82,8</t>
+          <t>76,36; 83,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,78; 22,85</t>
+          <t>14,53; 23,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62,24; 68,24</t>
+          <t>61,85; 67,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82,75; 86,92</t>
+          <t>82,75; 87,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,49; 78,73</t>
+          <t>73,38; 78,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,63; 20,74</t>
+          <t>15,91; 20,94</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,69; 47,4</t>
+          <t>34,73; 46,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,84; 69,74</t>
+          <t>59,22; 70,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,17; 56,73</t>
+          <t>45,54; 56,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 11,23</t>
+          <t>3,39; 11,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,2; 60,69</t>
+          <t>47,32; 60,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,0; 89,9</t>
+          <t>82,02; 90,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,37; 66,89</t>
+          <t>56,3; 67,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,13; 14,64</t>
+          <t>10,2; 14,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,31; 51,33</t>
+          <t>41,81; 51,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70,44; 77,64</t>
+          <t>70,8; 77,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52,15; 60,18</t>
+          <t>52,32; 60,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 12,09</t>
+          <t>5,98; 12,09</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,31; 29,03</t>
+          <t>13,44; 28,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37,06; 54,66</t>
+          <t>37,16; 54,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,82; 41,74</t>
+          <t>24,71; 41,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,63</t>
+          <t>3,98; 7,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,06; 41,64</t>
+          <t>28,7; 41,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,87; 52,58</t>
+          <t>38,03; 51,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,68; 38,23</t>
+          <t>23,19; 37,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,84</t>
+          <t>6,23; 9,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,14; 35,31</t>
+          <t>25,03; 35,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40,02; 50,61</t>
+          <t>40,19; 50,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,8; 36,01</t>
+          <t>25,9; 36,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,08</t>
+          <t>5,66; 8,13</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,71; 8,94</t>
+          <t>3,84; 9,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,08; 14,22</t>
+          <t>7,59; 15,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,65</t>
+          <t>5,27; 12,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,5</t>
+          <t>2,42; 5,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,74; 17,93</t>
+          <t>10,7; 17,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,8; 18,41</t>
+          <t>10,92; 18,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,69; 17,17</t>
+          <t>9,83; 17,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,07; 74,06</t>
+          <t>6,02; 71,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,24; 12,9</t>
+          <t>8,32; 12,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,98; 14,96</t>
+          <t>9,87; 15,29</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,53; 13,68</t>
+          <t>8,43; 13,46</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,95; 59,05</t>
+          <t>4,94; 59,57</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,61; 15,31</t>
+          <t>7,01; 14,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,82; 13,27</t>
+          <t>4,75; 13,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,9; 11,42</t>
+          <t>4,83; 10,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,81</t>
+          <t>4,7; 9,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,9; 12,03</t>
+          <t>5,77; 12,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,68; 15,18</t>
+          <t>8,7; 15,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,42; 17,7</t>
+          <t>9,66; 17,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,66; 9,27</t>
+          <t>5,73; 9,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,92; 11,98</t>
+          <t>7,03; 12,33</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,95; 13,22</t>
+          <t>8,15; 13,17</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,44; 13,95</t>
+          <t>8,44; 13,89</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,58</t>
+          <t>5,71; 8,49</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>34,72; 39,18</t>
+          <t>34,87; 39,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47,11; 51,56</t>
+          <t>47,11; 51,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41,86; 46,42</t>
+          <t>42,06; 46,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,84</t>
+          <t>6,04; 8,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>43,93; 47,96</t>
+          <t>44,12; 48,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,71; 63,48</t>
+          <t>59,51; 63,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,92; 53,39</t>
+          <t>49,1; 53,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,42; 32,69</t>
+          <t>11,38; 32,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40,34; 43,43</t>
+          <t>40,34; 43,48</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54,38; 57,44</t>
+          <t>54,27; 57,27</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46,46; 49,6</t>
+          <t>46,32; 49,57</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,46; 21,65</t>
+          <t>9,45; 20,25</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27844; 50940</t>
+          <t>28605; 50461</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42851; 66628</t>
+          <t>41748; 68910</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38369; 61930</t>
+          <t>37397; 62296</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4496; 24260</t>
+          <t>4008; 23937</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>51600; 77088</t>
+          <t>51353; 75911</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>104137; 133851</t>
+          <t>104739; 132882</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88991; 113665</t>
+          <t>89734; 114120</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12024; 35088</t>
+          <t>11111; 33407</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85228; 118631</t>
+          <t>85148; 119041</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>154728; 194592</t>
+          <t>152626; 190474</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>132853; 168875</t>
+          <t>132666; 170094</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20886; 48556</t>
+          <t>20945; 50222</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>161300; 196172</t>
+          <t>161204; 195826</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>198561; 235052</t>
+          <t>200213; 234041</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>179561; 208872</t>
+          <t>178295; 208258</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22556; 50321</t>
+          <t>22341; 51360</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>294280; 328411</t>
+          <t>295235; 328963</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>378541; 401263</t>
+          <t>378269; 401701</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>297800; 322405</t>
+          <t>299095; 322802</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52750; 106933</t>
+          <t>52224; 105444</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>467757; 514455</t>
+          <t>465538; 517280</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>587100; 630318</t>
+          <t>588534; 629190</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>484974; 525209</t>
+          <t>484373; 522791</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>86806; 145197</t>
+          <t>89825; 144737</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>286406; 328377</t>
+          <t>284426; 331836</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>401147; 443159</t>
+          <t>404524; 445557</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>310706; 352024</t>
+          <t>314358; 352789</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74180; 110805</t>
+          <t>73063; 110766</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>386077; 429970</t>
+          <t>385074; 431566</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>565834; 588687</t>
+          <t>567435; 588955</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>410725; 448135</t>
+          <t>413290; 449489</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87525; 135247</t>
+          <t>85998; 136778</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>684569; 750545</t>
+          <t>680254; 744192</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>975851; 1025009</t>
+          <t>975867; 1027941</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>739039; 791646</t>
+          <t>737890; 792094</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>176403; 234033</t>
+          <t>179564; 236256</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>103506; 137464</t>
+          <t>100729; 135830</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>220744; 261634</t>
+          <t>222162; 262739</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>153571; 192871</t>
+          <t>154830; 193381</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28192; 99658</t>
+          <t>30089; 100202</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>112353; 144469</t>
+          <t>112647; 143742</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>252323; 276634</t>
+          <t>252400; 277849</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>174881; 211264</t>
+          <t>177841; 213682</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>72185; 104372</t>
+          <t>72684; 104156</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>223408; 271083</t>
+          <t>220787; 270292</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>481039; 530174</t>
+          <t>483468; 531302</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>342021; 394688</t>
+          <t>343139; 396733</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>93805; 193459</t>
+          <t>95666; 193469</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14393; 31381</t>
+          <t>14529; 30771</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>52533; 77486</t>
+          <t>52673; 76972</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32328; 54355</t>
+          <t>32182; 54229</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22438; 42797</t>
+          <t>22339; 42611</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>56229; 83430</t>
+          <t>57515; 83800</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84114; 116798</t>
+          <t>84479; 115201</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48438; 78211</t>
+          <t>47447; 76060</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34524; 53939</t>
+          <t>34110; 52812</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>77546; 108931</t>
+          <t>77213; 108502</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>145615; 184150</t>
+          <t>146240; 185228</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86381; 120583</t>
+          <t>86702; 122389</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>61335; 89661</t>
+          <t>62750; 90189</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10855; 26153</t>
+          <t>11231; 27123</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21670; 43526</t>
+          <t>23219; 47123</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16320; 35022</t>
+          <t>15833; 36338</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8920; 20264</t>
+          <t>8903; 21136</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36729; 61316</t>
+          <t>36599; 61536</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37787; 64435</t>
+          <t>38222; 64565</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33534; 59442</t>
+          <t>34027; 58882</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36918; 450536</t>
+          <t>36600; 432411</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52311; 81886</t>
+          <t>52795; 80820</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65431; 98122</t>
+          <t>64705; 100299</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55196; 88485</t>
+          <t>54505; 87044</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>48322; 576650</t>
+          <t>48256; 581674</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13877; 32124</t>
+          <t>14702; 31210</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11943; 32893</t>
+          <t>11770; 32406</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12076; 28139</t>
+          <t>11886; 26919</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13404; 27740</t>
+          <t>13280; 26838</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>19705; 40167</t>
+          <t>19269; 40793</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33485; 58547</t>
+          <t>33550; 61029</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37095; 69701</t>
+          <t>38058; 67715</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>24094; 39489</t>
+          <t>24418; 39162</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37634; 65168</t>
+          <t>38215; 67028</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50352; 83772</t>
+          <t>51667; 83441</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54035; 89278</t>
+          <t>54011; 88944</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>40335; 60824</t>
+          <t>40491; 60187</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>663183; 748468</t>
+          <t>666019; 749273</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1006826; 1101905</t>
+          <t>1006836; 1105466</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>794075; 880538</t>
+          <t>797796; 881605</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>211217; 305947</t>
+          <t>209116; 305479</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1010970; 1103813</t>
+          <t>1015276; 1109391</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1502778; 1597594</t>
+          <t>1497883; 1594913</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1142237; 1246758</t>
+          <t>1146440; 1247762</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>423866; 1213729</t>
+          <t>422326; 1190097</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1698885; 1829024</t>
+          <t>1698777; 1830993</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2530825; 2673145</t>
+          <t>2525671; 2665308</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1966355; 2099250</t>
+          <t>1960395; 2097694</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>678344; 1552438</t>
+          <t>678095; 1452481</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,91; 26,31</t>
+          <t>14,37; 26,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,66; 39,05</t>
+          <t>23,77; 37,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,17; 40,26</t>
+          <t>24,4; 39,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,98</t>
+          <t>1,57; 6,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,06; 40,0</t>
+          <t>27,14; 40,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,31; 61,3</t>
+          <t>48,26; 61,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,29; 65,23</t>
+          <t>50,47; 65,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 10,67</t>
+          <t>4,26; 11,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,31; 31,2</t>
+          <t>22,49; 30,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,81; 48,43</t>
+          <t>38,76; 48,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40,24; 51,59</t>
+          <t>40,45; 51,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 7,04</t>
+          <t>3,54; 7,83</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,43; 63,69</t>
+          <t>52,38; 63,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,46; 73,02</t>
+          <t>62,33; 73,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,39; 79,89</t>
+          <t>68,86; 79,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 12,13</t>
+          <t>6,48; 13,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,41; 80,68</t>
+          <t>71,99; 80,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,05; 94,56</t>
+          <t>89,16; 94,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,45; 90,07</t>
+          <t>83,05; 89,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,2; 20,59</t>
+          <t>16,61; 23,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65,09; 72,33</t>
+          <t>64,9; 71,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78,96; 84,42</t>
+          <t>78,94; 84,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78,24; 84,45</t>
+          <t>78,24; 84,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 15,47</t>
+          <t>12,47; 17,81</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,73; 65,02</t>
+          <t>55,94; 64,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,02; 78,23</t>
+          <t>70,16; 78,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,69; 75,97</t>
+          <t>67,39; 75,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,62; 20,65</t>
+          <t>13,9; 20,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65,32; 73,21</t>
+          <t>65,29; 72,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>93,06; 96,59</t>
+          <t>92,72; 96,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,36; 83,05</t>
+          <t>76,15; 82,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,53; 23,1</t>
+          <t>19,23; 24,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61,85; 67,66</t>
+          <t>62,31; 67,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82,75; 87,16</t>
+          <t>82,87; 87,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,38; 78,77</t>
+          <t>73,34; 78,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,91; 20,94</t>
+          <t>17,59; 22,06</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,73; 46,83</t>
+          <t>35,58; 47,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,22; 70,03</t>
+          <t>59,79; 69,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,54; 56,88</t>
+          <t>45,63; 56,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,29</t>
+          <t>8,63; 13,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,32; 60,38</t>
+          <t>47,29; 60,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,02; 90,29</t>
+          <t>81,33; 90,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,3; 67,65</t>
+          <t>56,23; 67,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,2; 14,61</t>
+          <t>11,79; 15,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41,81; 51,18</t>
+          <t>42,35; 51,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70,8; 77,8</t>
+          <t>70,82; 77,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52,32; 60,49</t>
+          <t>52,03; 60,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,98; 12,09</t>
+          <t>10,92; 13,95</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,44; 28,47</t>
+          <t>12,74; 29,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37,16; 54,3</t>
+          <t>36,8; 54,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,71; 41,64</t>
+          <t>24,39; 40,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,59</t>
+          <t>4,09; 7,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,7; 41,82</t>
+          <t>28,28; 41,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,03; 51,86</t>
+          <t>38,97; 52,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,19; 37,18</t>
+          <t>24,03; 37,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,64</t>
+          <t>6,54; 10,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,03; 35,17</t>
+          <t>25,44; 35,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40,19; 50,9</t>
+          <t>40,02; 51,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,9; 36,55</t>
+          <t>25,69; 36,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,13</t>
+          <t>5,75; 8,35</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,84; 9,27</t>
+          <t>3,8; 9,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,59; 15,4</t>
+          <t>7,18; 14,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,27; 12,09</t>
+          <t>5,27; 11,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,74</t>
+          <t>2,61; 5,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,7; 17,99</t>
+          <t>10,74; 17,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,92; 18,45</t>
+          <t>10,58; 18,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,83; 17,01</t>
+          <t>9,47; 17,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,02; 71,08</t>
+          <t>5,55; 9,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,32; 12,74</t>
+          <t>7,94; 12,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,87; 15,29</t>
+          <t>9,88; 14,96</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,43; 13,46</t>
+          <t>8,71; 13,65</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,94; 59,57</t>
+          <t>4,48; 6,93</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,01; 14,87</t>
+          <t>6,75; 14,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,75; 13,08</t>
+          <t>4,61; 12,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,83; 10,93</t>
+          <t>4,91; 11,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,7; 9,49</t>
+          <t>4,84; 9,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,77; 12,22</t>
+          <t>5,72; 12,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,7; 15,82</t>
+          <t>8,73; 15,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,66; 17,19</t>
+          <t>9,57; 17,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,73; 9,2</t>
+          <t>5,48; 9,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,03; 12,33</t>
+          <t>7,06; 11,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,15; 13,17</t>
+          <t>7,86; 13,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,44; 13,89</t>
+          <t>8,52; 13,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,71; 8,49</t>
+          <t>5,65; 8,53</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>34,87; 39,22</t>
+          <t>34,77; 39,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47,11; 51,72</t>
+          <t>47,28; 51,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42,06; 46,48</t>
+          <t>42,21; 46,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,83</t>
+          <t>7,94; 9,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,12; 48,21</t>
+          <t>44,09; 48,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,51; 63,37</t>
+          <t>59,67; 63,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,1; 53,44</t>
+          <t>49,18; 53,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,38; 32,06</t>
+          <t>11,77; 13,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40,34; 43,48</t>
+          <t>40,25; 43,36</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54,27; 57,27</t>
+          <t>54,48; 57,5</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46,32; 49,57</t>
+          <t>46,66; 49,84</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,45; 20,25</t>
+          <t>10,22; 11,69</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>13652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>27335</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32335</t>
+          <t>40987</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28605; 50461</t>
+          <t>27565; 50601</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41748; 68910</t>
+          <t>41941; 66596</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37397; 62296</t>
+          <t>37752; 61312</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4008; 23937</t>
+          <t>6408; 27815</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>51353; 75911</t>
+          <t>51497; 76458</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>104739; 132882</t>
+          <t>104625; 132452</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89734; 114120</t>
+          <t>88298; 114915</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11111; 33407</t>
+          <t>15447; 43470</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85148; 119041</t>
+          <t>85807; 117762</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>152626; 190474</t>
+          <t>152421; 190678</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>132666; 170094</t>
+          <t>133347; 168907</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20945; 50222</t>
+          <t>27251; 60283</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33674</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>84638</t>
+          <t>99698</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>118312</t>
+          <t>145370</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>161204; 195826</t>
+          <t>161037; 196324</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>200213; 234041</t>
+          <t>199797; 235210</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>178295; 208258</t>
+          <t>179523; 207657</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22341; 51360</t>
+          <t>30918; 63375</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>295235; 328963</t>
+          <t>293512; 328191</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>378269; 401701</t>
+          <t>378744; 401940</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>299095; 322802</t>
+          <t>297647; 322360</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52224; 105444</t>
+          <t>83333; 118210</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>465538; 517280</t>
+          <t>464155; 514357</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>588534; 629190</t>
+          <t>588341; 631642</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>484373; 522791</t>
+          <t>484394; 524199</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>89825; 144737</t>
+          <t>122014; 174334</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90853</t>
+          <t>106312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>117549</t>
+          <t>137889</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>208402</t>
+          <t>244201</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>284426; 331836</t>
+          <t>285491; 328933</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>404524; 445557</t>
+          <t>399593; 444548</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314358; 352789</t>
+          <t>312942; 352571</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73063; 110766</t>
+          <t>86307; 126719</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>385074; 431566</t>
+          <t>384875; 429948</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>567435; 588955</t>
+          <t>565359; 587928</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>413290; 449489</t>
+          <t>412143; 448948</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>85998; 136778</t>
+          <t>119845; 155075</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>680254; 744192</t>
+          <t>685313; 746858</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>975867; 1027941</t>
+          <t>977266; 1026595</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>737890; 792094</t>
+          <t>737510; 790986</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>179564; 236256</t>
+          <t>218856; 274462</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66636</t>
+          <t>75830</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>88449</t>
+          <t>101470</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>155085</t>
+          <t>177300</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>100729; 135830</t>
+          <t>103204; 137557</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>222162; 262739</t>
+          <t>224328; 261854</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>154830; 193381</t>
+          <t>155138; 193472</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30089; 100202</t>
+          <t>60458; 94195</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>112647; 143742</t>
+          <t>112577; 143904</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>252400; 277849</t>
+          <t>250279; 276984</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>177841; 213682</t>
+          <t>177602; 211793</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>72684; 104156</t>
+          <t>86846; 117284</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>220787; 270292</t>
+          <t>223638; 270049</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>483468; 531302</t>
+          <t>483611; 531882</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>343139; 396733</t>
+          <t>341216; 393930</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>95666; 193469</t>
+          <t>156936; 200516</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31387</t>
+          <t>34793</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>42978</t>
+          <t>50104</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74365</t>
+          <t>84897</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14529; 30771</t>
+          <t>13776; 31409</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>52673; 76972</t>
+          <t>52169; 76816</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32182; 54229</t>
+          <t>31765; 53286</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22339; 42611</t>
+          <t>24929; 46903</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>57515; 83800</t>
+          <t>56667; 83519</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84479; 115201</t>
+          <t>86559; 117307</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47447; 76060</t>
+          <t>49168; 75811</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34110; 52812</t>
+          <t>39824; 61240</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>77213; 108502</t>
+          <t>78492; 110936</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>146240; 185228</t>
+          <t>145617; 186677</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86702; 122389</t>
+          <t>86002; 122675</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>62750; 90189</t>
+          <t>70021; 101761</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14053</t>
+          <t>15972</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>232082</t>
+          <t>31095</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>246135</t>
+          <t>47067</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11231; 27123</t>
+          <t>11107; 27000</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23219; 47123</t>
+          <t>21972; 45118</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15833; 36338</t>
+          <t>15846; 35182</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8903; 21136</t>
+          <t>10619; 23668</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36599; 61536</t>
+          <t>36727; 60359</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38222; 64565</t>
+          <t>37014; 64275</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34027; 58882</t>
+          <t>32797; 60757</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36600; 432411</t>
+          <t>24356; 40065</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52795; 80820</t>
+          <t>50407; 80230</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64705; 100299</t>
+          <t>64818; 98154</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>54505; 87044</t>
+          <t>56321; 88272</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>48256; 581674</t>
+          <t>37947; 58643</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19317</t>
+          <t>21007</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>30738</t>
+          <t>33048</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>50055</t>
+          <t>54055</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>14702; 31210</t>
+          <t>14167; 30821</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11770; 32406</t>
+          <t>11416; 31932</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11886; 26919</t>
+          <t>12090; 27304</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13280; 26838</t>
+          <t>15011; 29089</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>19269; 40793</t>
+          <t>19116; 41544</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33550; 61029</t>
+          <t>33676; 59914</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38058; 67715</t>
+          <t>37692; 68753</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>24418; 39162</t>
+          <t>25469; 42407</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>38215; 67028</t>
+          <t>38377; 65083</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51667; 83441</t>
+          <t>49769; 84560</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54011; 88944</t>
+          <t>54555; 88736</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>40491; 60187</t>
+          <t>43748; 66056</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>267516</t>
+          <t>313239</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>617174</t>
+          <t>480638</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>884690</t>
+          <t>793878</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>666019; 749273</t>
+          <t>664139; 750667</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1006836; 1105466</t>
+          <t>1010607; 1101968</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>797796; 881605</t>
+          <t>800754; 881590</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>209116; 305479</t>
+          <t>280385; 350896</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1015276; 1109391</t>
+          <t>1014719; 1108578</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1497883; 1594913</t>
+          <t>1501790; 1599144</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1146440; 1247762</t>
+          <t>1148280; 1246540</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>422326; 1190097</t>
+          <t>439680; 517265</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1698777; 1830993</t>
+          <t>1695103; 1826314</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2525671; 2665308</t>
+          <t>2535549; 2675987</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1960395; 2097694</t>
+          <t>1974561; 2109294</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>678095; 1452481</t>
+          <t>743311; 849666</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
